--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CBBCE0-582A-7048-A2F9-61740A14D0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0EBBA3-95DE-1040-8C3E-05B4F80085B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="3680" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>NO CLASS - Thanksgiving</t>
+  </si>
+  <si>
+    <t>00-Intro_to_Course</t>
+  </si>
+  <si>
+    <t>MMRgR3Wv37g</t>
   </si>
 </sst>
 </file>
@@ -672,6 +678,12 @@
       <c r="D2" t="s">
         <v>36</v>
       </c>
+      <c r="F2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
       <c r="H2" s="5"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0EBBA3-95DE-1040-8C3E-05B4F80085B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D106131-E722-6249-9DE1-05794784B21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="3680" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
   <si>
     <t>Date</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>MMRgR3Wv37g</t>
+  </si>
+  <si>
+    <t>01-Intro_to_Data</t>
+  </si>
+  <si>
+    <t>FM1VyknB1fs</t>
   </si>
 </sst>
 </file>
@@ -702,6 +708,12 @@
       <c r="E3" t="s">
         <v>47</v>
       </c>
+      <c r="F3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
       <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D106131-E722-6249-9DE1-05794784B21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D026D3-30C4-6B4D-883B-3012B5657DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="3680" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>FM1VyknB1fs</t>
+  </si>
+  <si>
+    <t>02-Summarizing_Data1</t>
   </si>
 </sst>
 </file>
@@ -734,6 +737,9 @@
         <v>48</v>
       </c>
       <c r="F4" s="8"/>
+      <c r="G4" t="s">
+        <v>68</v>
+      </c>
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D026D3-30C4-6B4D-883B-3012B5657DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF6DD22-591C-BA40-9150-C5DCF3C71C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="3680" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -242,6 +242,37 @@
   </si>
   <si>
     <t>02-Summarizing_Data1</t>
+  </si>
+  <si>
+    <t>dVGX-rAXFUQ</t>
+  </si>
+  <si>
+    <t>&lt;pre&gt;
+x &lt;- rnorm(500)
+sample_var &lt;- function(x) {
+	sum( (x - mean(x))^2)  / (length(x) - 1)
+}
+pop_var &lt;- function(x) {
+	sum( (x - mean(x))^2)  / (length(x))
+}
+# var(x)
+sample_var(x)
+pop_var(x)
+n &lt;- 5:500
+diff &lt;- numeric(length(x))
+for(i in n) {
+	x2 &lt;- x[1:i]
+	diff[i] &lt;- abs(sample_var(x2) - pop_var(x2))
+}
+diff
+library(ggplot2)
+ggplot(data.frame(x = 1:length(diff), y = diff), aes(x = x, y = y)) + geom_point()
+# What position are the vowels?
+letters
+vowels &lt;- c('a', 'e', 'i', 'o', 'u')
+letters %in% vowels
+letters %in% vowels |&gt; which()
+&lt;/pre&gt;</t>
   </si>
 </sst>
 </file>
@@ -719,7 +750,7 @@
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f>A3+7</f>
         <v>45908</v>
@@ -736,11 +767,15 @@
       <c r="E4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="8"/>
+      <c r="F4" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="G4" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF6DD22-591C-BA40-9150-C5DCF3C71C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC85CE5B-CB14-AE4D-B417-05E16716AE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="3680" windowWidth="19700" windowHeight="15960" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1680" yWindow="3680" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
   <si>
     <t>Date</t>
   </si>
@@ -273,6 +273,66 @@
 letters %in% vowels
 letters %in% vowels |&gt; which()
 &lt;/pre&gt;</t>
+  </si>
+  <si>
+    <t>install.packages('brickset')
+library(brickset)
+data("legosets")
+names(legosets)
+ggplot(legosets, aes(x = 'Lego', pieces)) +
+	geom_boxplot() +
+	geom_point(y = mean(legosets$pieces, na.rm= TRUE), color = 'blue', size = 4)
+	# scale_y_log10()
+mean(log(legosets$pieces + 1), na.rm = TRUE)
+log(mean(legosets$pieces, na.rm = TRUE)) - 1
+ggplot(legosets, aes(x = pieces, y = US_retailPrice, color = availability)) + 
+	geom_point(alpha = 0.1) +
+	theme_minimal()
+ggplot(legosets, aes(x = pieces, y = US_retailPrice)) + 
+	geom_point() +
+	theme_minimal()
+ggplot(legosets, aes(x = pieces, y = US_retailPrice)) + 
+	geom_point(color = 'purple') +
+	theme_minimal()
+ggplot(legosets, aes(x = US_retailPrice)) + geom_histogram()
+ggplot(legosets, aes(x = US_retailPrice)) + geom_histogram(binwidth = 25)
+ggplot(legosets, aes(x = US_retailPrice)) + geom_histogram(bins = 100)
+ggplot(legosets, aes(x = US_retailPrice)) + geom_density()
+x &lt;- seq(0, 1000, by = 0.1)
+df &lt;- data.frame(x = x, y = log(x))
+ggplot(df, aes(x = x, y = y)) + geom_path() + geom_point()
+# https://nycbirdalliance.org/rails/active_storage/disk/eyJfcmFpbHMiOnsibWVzc2FnZSI6IkJBaDdDRG9JYTJWNVNTSnJkbUZ5YVdGdWRITXZPRzVqZGpBMGNERjNlbTUwWkd0cVlXbzJhV0UxZDJ0MGRUTnVaUzgzTm1FNFkyWTRPVGxpWW1ZeFlUZzBPREl5WTJWaVlURmpNVEV6WVdNM1pqRmlaR0kyWW1Wa1ltTTBNVEl4TVRWbVl6azFaV016TVRZeU1tTXdaR0pqQmpvR1JWUTZFR1JwYzNCdmMybDBhVzl1U1NKeGFXNXNhVzVsT3lCbWFXeGxibUZ0WlQwaWFIVnRZVzR0Y21Wc1lYUmxaRjlpYVhKa1gyUmxZWFJvYzE5bWFXNWhiQzV3Ym1jaU95Qm1hV3hsYm1GdFpTbzlWVlJHTFRnbkoyaDFiV0Z1TFhKbGJHRjBaV1JmWW1seVpGOWtaV0YwYUhOZlptbHVZV3d1Y0c1bkJqc0dWRG9SWTI5dWRHVnVkRjkwZVhCbFNTSU9hVzFoWjJVdmNHNW5CanNHVkE9PSIsImV4cCI6IjIwMjUtMDktMTZUMDA6NTI6NTMuNTcyWiIsInB1ciI6ImJsb2Jfa2V5In19--240aa3bfaa08f359b0e9a01e831ff7fd77117e64/human-related_bird_deaths_final.png?content_type=image%2Fpng&amp;disposition=inline%3B+filename%3D%22human-related_bird_deaths_final.png%22%3B+filename%2A%3DUTF-8%27%27human-related_bird_deaths_final.png
+birds &lt;- data.frame(
+	category = c('Collisions with vehicles',
+	  'Poison', 
+	  'Collisions with electrical lines',
+	  'Electrocution',
+	  'Oil pits',
+	  'Collisions wind turbines',
+	  'Collisions with building glass',
+	  'Cats'),
+	deaths = c(214500000,
+			   7200000,
+			   32500000,
+			   6250000,
+			   750000,
+			   328000,
+			   676500000,
+			   1850700000)
+)
+library(xkcd)
+ggplot(birds, aes(x = category, y = deaths)) + 
+	geom_bar(stat = 'identity') +
+	coord_flip() +
+	xlab('') +
+	ylab('Number of deaths') +
+	theme_minimal()</t>
+  </si>
+  <si>
+    <t>02-Summarizing_Data2</t>
+  </si>
+  <si>
+    <t>gh51jHFKR3c</t>
   </si>
 </sst>
 </file>
@@ -750,7 +810,7 @@
       </c>
       <c r="H3" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f>A3+7</f>
         <v>45908</v>
@@ -777,7 +837,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A17" si="0">A4+7</f>
         <v>45915</v>
@@ -794,7 +854,15 @@
       <c r="E5" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="F5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC85CE5B-CB14-AE4D-B417-05E16716AE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187FA0D2-3933-2C40-B413-FBB417641DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1680" yWindow="3680" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="1060" yWindow="8200" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
   <si>
     <t>Date</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>gh51jHFKR3c</t>
+  </si>
+  <si>
+    <t>03-Probablity</t>
+  </si>
+  <si>
+    <t>l2pq8u66S-o</t>
   </si>
 </sst>
 </file>
@@ -837,7 +843,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A17" si="0">A4+7</f>
         <v>45915</v>
@@ -881,7 +887,12 @@
       <c r="E6" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" t="s">
+        <v>74</v>
+      </c>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187FA0D2-3933-2C40-B413-FBB417641DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B164294B-10B0-0545-A81E-0109978F8765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="8200" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -335,10 +335,10 @@
     <t>gh51jHFKR3c</t>
   </si>
   <si>
-    <t>03-Probablity</t>
-  </si>
-  <si>
     <t>l2pq8u66S-o</t>
+  </si>
+  <si>
+    <t>03-Probability</t>
   </si>
 </sst>
 </file>
@@ -888,10 +888,10 @@
         <v>49</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" t="s">
         <v>75</v>
-      </c>
-      <c r="G6" t="s">
-        <v>74</v>
       </c>
       <c r="H6" s="4"/>
     </row>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B164294B-10B0-0545-A81E-0109978F8765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A651F67F-CB00-6E43-AF80-AC7A0EAC7727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="8200" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="78">
   <si>
     <t>Date</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>03-Probability</t>
+  </si>
+  <si>
+    <t>04-Distributions</t>
+  </si>
+  <si>
+    <t>r4fAZTNbpys</t>
   </si>
 </sst>
 </file>
@@ -912,6 +918,12 @@
       <c r="E7" t="s">
         <v>50</v>
       </c>
+      <c r="F7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" t="s">
+        <v>76</v>
+      </c>
       <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A651F67F-CB00-6E43-AF80-AC7A0EAC7727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6C8073-7EFB-AA41-A0E2-6F0EB4ECE630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="8200" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="80">
   <si>
     <t>Date</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>r4fAZTNbpys</t>
+  </si>
+  <si>
+    <t>05-Foundation_for_Inference</t>
+  </si>
+  <si>
+    <t>q-FD8o9X72Q</t>
   </si>
 </sst>
 </file>
@@ -943,6 +949,12 @@
       <c r="E8" t="s">
         <v>51</v>
       </c>
+      <c r="F8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" t="s">
+        <v>78</v>
+      </c>
       <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6C8073-7EFB-AA41-A0E2-6F0EB4ECE630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56032035-4F3A-0844-B69E-FAEF9C112BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="8200" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="10860" yWindow="8700" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
   <si>
     <t>Date</t>
   </si>
@@ -351,6 +351,12 @@
   </si>
   <si>
     <t>q-FD8o9X72Q</t>
+  </si>
+  <si>
+    <t>06-Inference_for_Categorical_Data</t>
+  </si>
+  <si>
+    <t>UAlxCPaAD0g</t>
   </si>
 </sst>
 </file>
@@ -974,6 +980,12 @@
       <c r="E9" t="s">
         <v>52</v>
       </c>
+      <c r="F9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" t="s">
+        <v>80</v>
+      </c>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56032035-4F3A-0844-B69E-FAEF9C112BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5DA898-3D38-7949-B376-CAA94E4EDADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10860" yWindow="8700" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="600" yWindow="10460" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>UAlxCPaAD0g</t>
+  </si>
+  <si>
+    <t>07-Inference_for_Numerical_Data</t>
+  </si>
+  <si>
+    <t>_0dqhgtsNgQ</t>
   </si>
 </sst>
 </file>
@@ -1005,6 +1011,12 @@
       <c r="E10" t="s">
         <v>53</v>
       </c>
+      <c r="F10" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" t="s">
+        <v>82</v>
+      </c>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5DA898-3D38-7949-B376-CAA94E4EDADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413B9055-F820-CE40-8F8B-783EBBA0F492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="10460" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
   <si>
     <t>Date</t>
   </si>
@@ -363,6 +363,12 @@
   </si>
   <si>
     <t>_0dqhgtsNgQ</t>
+  </si>
+  <si>
+    <t>08-Linear_Regression</t>
+  </si>
+  <si>
+    <t>RNRmcDEwmSA</t>
   </si>
 </sst>
 </file>
@@ -1036,6 +1042,12 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
+      <c r="F11" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" t="s">
+        <v>84</v>
+      </c>
       <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413B9055-F820-CE40-8F8B-783EBBA0F492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B0A274-121E-4046-88F3-998184F48285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="10460" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="88">
   <si>
     <t>Date</t>
   </si>
@@ -369,6 +369,12 @@
   </si>
   <si>
     <t>RNRmcDEwmSA</t>
+  </si>
+  <si>
+    <t>08-Linear_Regression2</t>
+  </si>
+  <si>
+    <t>I6EWsPvfUZs</t>
   </si>
 </sst>
 </file>
@@ -1067,6 +1073,12 @@
       <c r="E12" t="s">
         <v>54</v>
       </c>
+      <c r="F12" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s">
+        <v>86</v>
+      </c>
       <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B0A274-121E-4046-88F3-998184F48285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACFA55F-CAE3-F34B-8B0D-E9D3CCED7BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="10460" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="760" yWindow="11220" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="90">
   <si>
     <t>Date</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>I6EWsPvfUZs</t>
+  </si>
+  <si>
+    <t>09-Logistic_Regression</t>
+  </si>
+  <si>
+    <t>Zma5A7QGN30</t>
   </si>
 </sst>
 </file>
@@ -1098,6 +1104,12 @@
       <c r="E13" t="s">
         <v>55</v>
       </c>
+      <c r="F13" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACFA55F-CAE3-F34B-8B0D-E9D3CCED7BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCE358-CCE3-5443-B2A4-2159DCFB0AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="11220" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>Date</t>
   </si>
@@ -381,6 +381,12 @@
   </si>
   <si>
     <t>Zma5A7QGN30</t>
+  </si>
+  <si>
+    <t>09-Multiple_Regression</t>
+  </si>
+  <si>
+    <t>ZnFGon11A38</t>
   </si>
 </sst>
 </file>
@@ -1126,6 +1132,15 @@
       <c r="D14" t="s">
         <v>33</v>
       </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>90</v>
+      </c>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1135,9 +1150,6 @@
       </c>
       <c r="D15" t="s">
         <v>63</v>
-      </c>
-      <c r="E15" t="s">
-        <v>55</v>
       </c>
       <c r="H15" s="4"/>
     </row>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EFCE358-CCE3-5443-B2A4-2159DCFB0AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB4C3B0-CDFC-F144-9DD3-59FEDD9D6D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="11220" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
+    <workbookView xWindow="5660" yWindow="9180" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
   <sheets>
     <sheet name="Meetups" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="94">
   <si>
     <t>Date</t>
   </si>
@@ -387,6 +387,12 @@
   </si>
   <si>
     <t>ZnFGon11A38</t>
+  </si>
+  <si>
+    <t>10-Bayesian_Analysis</t>
+  </si>
+  <si>
+    <t>SmpqWqB4ToM</t>
   </si>
 </sst>
 </file>
@@ -1170,6 +1176,12 @@
       <c r="E16" t="s">
         <v>56</v>
       </c>
+      <c r="F16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G16" t="s">
+        <v>92</v>
+      </c>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/SPS Dropbox/Jason Bryer/Teaching/DATA606 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB4C3B0-CDFC-F144-9DD3-59FEDD9D6D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A300849E-C062-7D42-893B-C22E24534EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5660" yWindow="9180" windowWidth="28760" windowHeight="16060" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -393,6 +393,12 @@
   </si>
   <si>
     <t>SmpqWqB4ToM</t>
+  </si>
+  <si>
+    <t>11-Final_Meetup</t>
+  </si>
+  <si>
+    <t>-slrOq6AG_0</t>
   </si>
 </sst>
 </file>
@@ -1198,6 +1204,12 @@
       <c r="D17" t="s">
         <v>35</v>
       </c>
+      <c r="F17" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" t="s">
+        <v>94</v>
+      </c>
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
